--- a/resources/data-imports/Monsters/weekly-monsters-shadow-planes.xlsx
+++ b/resources/data-imports/Monsters/weekly-monsters-shadow-planes.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -394,34 +394,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -567,7 +567,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.71"/>
@@ -833,7 +833,7 @@
         <v>0.005214630605232</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>515785385.834944</v>
+        <v>4000000</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0.00687503156550513</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>568210276.658055</v>
+        <v>4931609</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>0.00906412411634075</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>625963680.566829</v>
+        <v>6080192</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v>0.011950250004473</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>689587192.426954</v>
+        <v>7496283</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0.0157553530088973</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>759677455.293703</v>
+        <v>9242185</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0.0207720464711663</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>836891755.559465</v>
+        <v>11394711</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0.0273861153321433</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>921954186.797109</v>
+        <v>14048565</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0.0361061830872817</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1015662440.10194</v>
+        <v>17320508</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0.0476028250564693</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1118895284.61009</v>
+        <v>21354494</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
         <v>0.0627601357883498</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1232620808.34362</v>
+        <v>26328005</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>0</v>
@@ -2044,7 +2044,7 @@
         <v>0.0827437161449898</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>1357905496.66239</v>
+        <v>32459858</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
         <v>0.109090308290148</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>1495924233.4581</v>
+        <v>40019834</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0.143825971533431</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>1647971318.87859</v>
+        <v>49340545</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         <v>0.189621886781334</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>1815472606.9036</v>
+        <v>60832072</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0.249999770995152</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1999998876.59463</v>
+        <v>75000001</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>0</v>
